--- a/data/05_modelado/results/results_boosting.xlsx
+++ b/data/05_modelado/results/results_boosting.xlsx
@@ -563,10 +563,10 @@
         <v>0.9060825902190193</v>
       </c>
       <c r="K2" t="n">
-        <v>16.899</v>
+        <v>7.719</v>
       </c>
       <c r="L2" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="M2" t="n">
         <v>0.8336</v>
@@ -628,10 +628,10 @@
         <v>0.8938130869670085</v>
       </c>
       <c r="K3" t="n">
-        <v>10.126</v>
+        <v>6.945</v>
       </c>
       <c r="L3" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="M3" t="n">
         <v>0.8298</v>
@@ -693,10 +693,10 @@
         <v>0.9034056232726609</v>
       </c>
       <c r="K4" t="n">
-        <v>8.996</v>
+        <v>5.541</v>
       </c>
       <c r="L4" t="n">
-        <v>6.65</v>
+        <v>6.64</v>
       </c>
       <c r="M4" t="n">
         <v>0.829</v>
@@ -758,7 +758,7 @@
         <v>0.9037402095855354</v>
       </c>
       <c r="K5" t="n">
-        <v>25.148</v>
+        <v>4.319</v>
       </c>
       <c r="L5" t="n">
         <v>6.65</v>
@@ -823,7 +823,7 @@
         <v>0.8915822788746819</v>
       </c>
       <c r="K6" t="n">
-        <v>16.487</v>
+        <v>6.472</v>
       </c>
       <c r="L6" t="n">
         <v>6.65</v>
@@ -888,7 +888,7 @@
         <v>0.9013234725985884</v>
       </c>
       <c r="K7" t="n">
-        <v>19.148</v>
+        <v>5.949</v>
       </c>
       <c r="L7" t="n">
         <v>6.65</v>
@@ -953,10 +953,10 @@
         <v>0.8904668851951449</v>
       </c>
       <c r="K8" t="n">
-        <v>34.533</v>
+        <v>16.095</v>
       </c>
       <c r="L8" t="n">
-        <v>6.64</v>
+        <v>6.77</v>
       </c>
       <c r="M8" t="n">
         <v>0.8188</v>
@@ -1018,7 +1018,7 @@
         <v>0.9016952267215682</v>
       </c>
       <c r="K9" t="n">
-        <v>27.511</v>
+        <v>13.655</v>
       </c>
       <c r="L9" t="n">
         <v>6.63</v>
@@ -1083,7 +1083,7 @@
         <v>0.8993900899201147</v>
       </c>
       <c r="K10" t="n">
-        <v>47.524</v>
+        <v>18.953</v>
       </c>
       <c r="L10" t="n">
         <v>6.64</v>
@@ -1148,10 +1148,10 @@
         <v>0.8948169219275567</v>
       </c>
       <c r="K11" t="n">
-        <v>42.487</v>
+        <v>32.164</v>
       </c>
       <c r="L11" t="n">
-        <v>6.92</v>
+        <v>6.91</v>
       </c>
       <c r="M11" t="n">
         <v>0.8159999999999999</v>
@@ -1213,7 +1213,7 @@
         <v>0.8948169219275567</v>
       </c>
       <c r="K12" t="n">
-        <v>26.029</v>
+        <v>14.979</v>
       </c>
       <c r="L12" t="n">
         <v>6.65</v>
@@ -1278,10 +1278,10 @@
         <v>0.8910245751238295</v>
       </c>
       <c r="K13" t="n">
-        <v>73.32599999999999</v>
+        <v>25.285</v>
       </c>
       <c r="L13" t="n">
-        <v>6.79</v>
+        <v>6.65</v>
       </c>
       <c r="M13" t="n">
         <v>0.8163</v>

--- a/data/05_modelado/results/results_boosting.xlsx
+++ b/data/05_modelado/results/results_boosting.xlsx
@@ -563,7 +563,7 @@
         <v>0.9060825902190193</v>
       </c>
       <c r="K2" t="n">
-        <v>7.719</v>
+        <v>5.81</v>
       </c>
       <c r="L2" t="n">
         <v>6.64</v>
@@ -628,7 +628,7 @@
         <v>0.8938130869670085</v>
       </c>
       <c r="K3" t="n">
-        <v>6.945</v>
+        <v>5.958</v>
       </c>
       <c r="L3" t="n">
         <v>6.64</v>
@@ -693,7 +693,7 @@
         <v>0.9034056232726609</v>
       </c>
       <c r="K4" t="n">
-        <v>5.541</v>
+        <v>5.582</v>
       </c>
       <c r="L4" t="n">
         <v>6.64</v>
@@ -758,10 +758,10 @@
         <v>0.9037402095855354</v>
       </c>
       <c r="K5" t="n">
-        <v>4.319</v>
+        <v>11.247</v>
       </c>
       <c r="L5" t="n">
-        <v>6.65</v>
+        <v>6.79</v>
       </c>
       <c r="M5" t="n">
         <v>0.8334</v>
@@ -823,7 +823,7 @@
         <v>0.8915822788746819</v>
       </c>
       <c r="K6" t="n">
-        <v>6.472</v>
+        <v>9.07</v>
       </c>
       <c r="L6" t="n">
         <v>6.65</v>
@@ -888,7 +888,7 @@
         <v>0.9013234725985884</v>
       </c>
       <c r="K7" t="n">
-        <v>5.949</v>
+        <v>10.553</v>
       </c>
       <c r="L7" t="n">
         <v>6.65</v>
@@ -953,10 +953,10 @@
         <v>0.8904668851951449</v>
       </c>
       <c r="K8" t="n">
-        <v>16.095</v>
+        <v>25.825</v>
       </c>
       <c r="L8" t="n">
-        <v>6.77</v>
+        <v>6.63</v>
       </c>
       <c r="M8" t="n">
         <v>0.8188</v>
@@ -1018,7 +1018,7 @@
         <v>0.9016952267215682</v>
       </c>
       <c r="K9" t="n">
-        <v>13.655</v>
+        <v>25.352</v>
       </c>
       <c r="L9" t="n">
         <v>6.63</v>
@@ -1083,7 +1083,7 @@
         <v>0.8993900899201147</v>
       </c>
       <c r="K10" t="n">
-        <v>18.953</v>
+        <v>32.373</v>
       </c>
       <c r="L10" t="n">
         <v>6.64</v>
@@ -1148,7 +1148,7 @@
         <v>0.8948169219275567</v>
       </c>
       <c r="K11" t="n">
-        <v>32.164</v>
+        <v>9.906000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>6.91</v>
@@ -1213,7 +1213,7 @@
         <v>0.8948169219275567</v>
       </c>
       <c r="K12" t="n">
-        <v>14.979</v>
+        <v>18.66</v>
       </c>
       <c r="L12" t="n">
         <v>6.65</v>
@@ -1278,7 +1278,7 @@
         <v>0.8910245751238295</v>
       </c>
       <c r="K13" t="n">
-        <v>25.285</v>
+        <v>21.543</v>
       </c>
       <c r="L13" t="n">
         <v>6.65</v>
